--- a/plantilla_entrada.xlsx
+++ b/plantilla_entrada.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,6 +481,36 @@
       </c>
       <c r="F2" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BBB020202BBB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Proveedor de Ejemplo SA de CV</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2015-01-10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>64000</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
